--- a/base/StructureDefinition-SGLibrary.xlsx
+++ b/base/StructureDefinition-SGLibrary.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1658" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1658" uniqueCount="363">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-02T12:10:23+02:00</t>
+    <t>2026-08-27T08:35:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -269,7 +269,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}lib-0:Name should be usable as an identifier for the module by machine processing applications such as code generation {name.matches('[A-Z]([A-Za-z0-9_]){0,254}')}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}lib-0:Name should be usable as an identifier for the module by machine processing applications such as code generation {name.matches('[A-Z]([A-Za-z0-9_]){0,254}')}shr-1:If knowledge capabilities are stated, they SHALL include shareable {extension('http://hl7.org/fhir/StructureDefinition/cqf-knowledgeCapability').exists() implies extension('http://hl7.org/fhir/StructureDefinition/cqf-knowledgeCapability').where(value = 'shareable').exists()}</t>
   </si>
   <si>
     <t>Act[classCode=GROUPER;moodCode=EVN]</t>
@@ -358,7 +358,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -459,20 +459,8 @@
     <t>Defines a knowledge capability afforded by this knowledge artifact.</t>
   </si>
   <si>
-    <t>Library.extension:artifactComment</t>
-  </si>
-  <si>
-    <t>artifactComment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {cqf-artifactComment}
-</t>
-  </si>
-  <si>
-    <t>Additional documentation, review, or usage guidance</t>
-  </si>
-  <si>
-    <t>A comment containing additional documentation, a review comment, usage guidance, or other relevant information from a particular user.</t>
+    <t>ele-1
+shr-1</t>
   </si>
   <si>
     <t>Library.extension:versionAlgorithm</t>
@@ -494,6 +482,10 @@
     <t>If set as a string, this is a FHIRPath expression that has two additional context variables passed in - %version1 and %version2 and will return a negative number if version1 is newer, a positive number if version2 and a 0 if the version ordering can't be successfully be determined.</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
     <t>Library.extension:versionPolicy</t>
   </si>
   <si>
@@ -508,6 +500,22 @@
   </si>
   <si>
     <t>Defines the versioning policy of the artifact.</t>
+  </si>
+  <si>
+    <t>Library.extension:webSource</t>
+  </si>
+  <si>
+    <t>webSource</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {web-source}
+</t>
+  </si>
+  <si>
+    <t>web-source</t>
+  </si>
+  <si>
+    <t>Where a human readable web page describing the resource can be found, if it's at a different location to the canonical URL itself.</t>
   </si>
   <si>
     <t>Library.modifierExtension</t>
@@ -732,7 +740,7 @@
     <t>The type of knowledge asset this library contains.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/library-type</t>
+    <t>http://hl7.org/fhir/ValueSet/library-type|4.0.1</t>
   </si>
   <si>
     <t>.code</t>
@@ -745,7 +753,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(Group)</t>
+Reference(Group|4.0.1)</t>
   </si>
   <si>
     <t>Type of individual the library content is focused on</t>
@@ -760,7 +768,7 @@
     <t>The possible types of subjects for a library (E.g. Patient, Practitioner, Organization, Location, etc.).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/subject-type</t>
+    <t>http://hl7.org/fhir/ValueSet/subject-type|4.0.1</t>
   </si>
   <si>
     <t>Library.date</t>
@@ -897,7 +905,7 @@
     <t>Countries and regions within which this artifact is targeted for use.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/jurisdiction</t>
+    <t>http://hl7.org/fhir/ValueSet/jurisdiction|4.0.1</t>
   </si>
   <si>
     <t>Definition.jurisdiction</t>
@@ -1035,7 +1043,7 @@
     <t>High-level categorization of the definition, used for searching, sorting, and filtering.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/definition-topic</t>
+    <t>http://hl7.org/fhir/ValueSet/definition-topic|4.0.1</t>
   </si>
   <si>
     <t>Library.author</t>
@@ -1458,17 +1466,17 @@
   <dimension ref="A1:AN45"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="35.6796875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="24.07421875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="19.65234375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="38.81640625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.90234375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.69921875" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.07421875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="14.625" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="11.98828125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="31.50390625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="21.13671875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="17.2890625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="34.17578125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="30.79296875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1477,26 +1485,26 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="8.84375" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="15.71484375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="16.08984375" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="17.078125" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.3125" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="88.19140625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="48.51953125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.69140625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="19.73046875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.8203125" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="14.98828125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="12.3046875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="33.1484375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.5" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.87890625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="78.34375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="41.1171875" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="29.0546875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="129.28125" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="26.71875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="32.84375" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="43.078125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="114.75" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="41.19921875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2525,7 +2533,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>137</v>
       </c>
@@ -2621,7 +2629,7 @@
         <v>82</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>20</v>
+        <v>142</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>136</v>
@@ -2639,15 +2647,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B11" t="s" s="2">
         <v>129</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>20</v>
@@ -2657,7 +2665,7 @@
         <v>81</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>86</v>
@@ -2669,15 +2677,17 @@
         <v>20</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="N11" s="2"/>
+        <v>147</v>
+      </c>
+      <c r="N11" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>20</v>
@@ -2735,7 +2745,7 @@
         <v>82</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>20</v>
+        <v>149</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>136</v>
@@ -2755,13 +2765,13 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>129</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>20</v>
@@ -2774,7 +2784,7 @@
         <v>77</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>20</v>
@@ -2783,17 +2793,15 @@
         <v>20</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="N12" s="2"/>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>20</v>
@@ -2851,7 +2859,7 @@
         <v>82</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>20</v>
+        <v>149</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>136</v>
@@ -2869,15 +2877,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B13" t="s" s="2">
         <v>129</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D13" t="s" s="2">
         <v>20</v>
@@ -2899,13 +2907,13 @@
         <v>20</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2965,7 +2973,7 @@
         <v>82</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>20</v>
+        <v>149</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>136</v>
@@ -2985,14 +2993,14 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -3014,16 +3022,16 @@
         <v>130</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>20</v>
@@ -3072,7 +3080,7 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>81</v>
@@ -3099,12 +3107,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3130,16 +3138,16 @@
         <v>99</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>20</v>
@@ -3188,7 +3196,7 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>81</v>
@@ -3203,13 +3211,13 @@
         <v>97</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>20</v>
@@ -3217,10 +3225,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3243,19 +3251,19 @@
         <v>86</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>20</v>
@@ -3304,7 +3312,7 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>81</v>
@@ -3319,24 +3327,24 @@
         <v>97</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
-    <row r="17" hidden="true">
+    <row r="17">
       <c r="A17" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3359,16 +3367,16 @@
         <v>86</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3418,7 +3426,7 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -3433,24 +3441,24 @@
         <v>97</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3473,19 +3481,19 @@
         <v>86</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>20</v>
@@ -3534,7 +3542,7 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -3543,7 +3551,7 @@
         <v>77</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AJ18" t="s" s="2">
         <v>97</v>
@@ -3561,12 +3569,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3589,16 +3597,16 @@
         <v>86</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3648,7 +3656,7 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -3663,10 +3671,10 @@
         <v>97</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>20</v>
@@ -3677,10 +3685,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3703,13 +3711,13 @@
         <v>20</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3760,7 +3768,7 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -3787,12 +3795,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3818,13 +3826,13 @@
         <v>105</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3850,13 +3858,13 @@
         <v>20</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>20</v>
@@ -3874,7 +3882,7 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
@@ -3889,24 +3897,24 @@
         <v>97</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3929,19 +3937,19 @@
         <v>86</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>20</v>
@@ -3990,7 +3998,7 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -4005,13 +4013,13 @@
         <v>97</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>20</v>
@@ -4019,10 +4027,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4045,13 +4053,13 @@
         <v>86</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4078,13 +4086,13 @@
         <v>20</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>20</v>
@@ -4102,7 +4110,7 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
@@ -4117,13 +4125,13 @@
         <v>97</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>20</v>
@@ -4131,10 +4139,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4157,13 +4165,13 @@
         <v>20</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4171,7 +4179,7 @@
         <v>20</v>
       </c>
       <c r="Q24" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="R24" t="s" s="2">
         <v>20</v>
@@ -4192,13 +4200,13 @@
         <v>20</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>20</v>
@@ -4216,7 +4224,7 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -4245,14 +4253,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4271,16 +4279,16 @@
         <v>86</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4330,7 +4338,7 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -4345,24 +4353,24 @@
         <v>97</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4385,19 +4393,19 @@
         <v>86</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>20</v>
@@ -4446,7 +4454,7 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -4461,13 +4469,13 @@
         <v>97</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>20</v>
@@ -4475,10 +4483,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4501,16 +4509,16 @@
         <v>86</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4560,7 +4568,7 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -4575,10 +4583,10 @@
         <v>97</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>20</v>
@@ -4587,12 +4595,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4615,16 +4623,16 @@
         <v>86</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4674,7 +4682,7 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -4689,10 +4697,10 @@
         <v>97</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>20</v>
@@ -4703,10 +4711,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4729,19 +4737,19 @@
         <v>86</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>20</v>
@@ -4790,7 +4798,7 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -4805,10 +4813,10 @@
         <v>97</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>20</v>
@@ -4819,10 +4827,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4845,16 +4853,16 @@
         <v>86</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4880,13 +4888,13 @@
         <v>20</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>20</v>
@@ -4904,7 +4912,7 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -4919,10 +4927,10 @@
         <v>97</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>20</v>
@@ -4933,10 +4941,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4959,16 +4967,16 @@
         <v>20</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5018,7 +5026,7 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5033,24 +5041,24 @@
         <v>97</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5073,13 +5081,13 @@
         <v>20</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5130,7 +5138,7 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5145,7 +5153,7 @@
         <v>97</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>20</v>
@@ -5159,14 +5167,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5185,17 +5193,17 @@
         <v>20</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>20</v>
@@ -5244,7 +5252,7 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -5259,24 +5267,24 @@
         <v>97</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5299,16 +5307,16 @@
         <v>20</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5358,7 +5366,7 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -5373,24 +5381,24 @@
         <v>97</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5413,19 +5421,19 @@
         <v>20</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>20</v>
@@ -5474,7 +5482,7 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -5489,24 +5497,24 @@
         <v>97</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5529,19 +5537,19 @@
         <v>86</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>20</v>
@@ -5590,7 +5598,7 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -5605,24 +5613,24 @@
         <v>97</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5645,17 +5653,17 @@
         <v>20</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>20</v>
@@ -5680,13 +5688,13 @@
         <v>20</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>20</v>
@@ -5704,7 +5712,7 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -5719,7 +5727,7 @@
         <v>97</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>20</v>
@@ -5733,10 +5741,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5759,13 +5767,13 @@
         <v>20</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5816,7 +5824,7 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -5831,7 +5839,7 @@
         <v>97</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>20</v>
@@ -5845,10 +5853,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5871,13 +5879,13 @@
         <v>20</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5928,7 +5936,7 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -5957,10 +5965,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5983,13 +5991,13 @@
         <v>20</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6040,7 +6048,7 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -6055,7 +6063,7 @@
         <v>97</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>20</v>
@@ -6069,10 +6077,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6095,13 +6103,13 @@
         <v>20</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6152,7 +6160,7 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -6167,7 +6175,7 @@
         <v>97</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>20</v>
@@ -6181,10 +6189,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6207,19 +6215,19 @@
         <v>20</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>20</v>
@@ -6268,7 +6276,7 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -6283,7 +6291,7 @@
         <v>97</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>20</v>
@@ -6297,10 +6305,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6323,13 +6331,13 @@
         <v>20</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6380,7 +6388,7 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -6395,7 +6403,7 @@
         <v>97</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>20</v>
@@ -6409,10 +6417,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6435,13 +6443,13 @@
         <v>20</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6492,7 +6500,7 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -6507,7 +6515,7 @@
         <v>97</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>20</v>
@@ -6521,10 +6529,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6547,13 +6555,13 @@
         <v>86</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6604,7 +6612,7 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -6619,7 +6627,7 @@
         <v>97</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>20</v>
@@ -6633,12 +6641,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AN45">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
